--- a/Storage_Data.xlsx
+++ b/Storage_Data.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevingransee/Library/Mobile Documents/com~apple~CloudDocs/Master_thesis/CDR_min_cost/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\MC-CDR_Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9BE3A7-92DF-6245-B2DF-98F047F97554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F55AB86-A7E4-476A-B05B-353F1D20D9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{7C28435E-2221-7246-93CD-80D5B3BE1736}"/>
+    <workbookView xWindow="-28920" yWindow="-1050" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{7C28435E-2221-7246-93CD-80D5B3BE1736}"/>
   </bookViews>
   <sheets>
     <sheet name="Europe" sheetId="1" r:id="rId1"/>
     <sheet name="NorthAm" sheetId="13" r:id="rId2"/>
+    <sheet name="Global" sheetId="14" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,16 +29,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="423">
   <si>
     <t>Sweden</t>
   </si>
@@ -238,13 +240,1081 @@
   </si>
   <si>
     <t>United States of America</t>
+  </si>
+  <si>
+    <t>AFG</t>
+  </si>
+  <si>
+    <t>Afghanistan</t>
+  </si>
+  <si>
+    <t>BGD</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>BRN</t>
+  </si>
+  <si>
+    <t>Brunei Darussalam</t>
+  </si>
+  <si>
+    <t>BTN</t>
+  </si>
+  <si>
+    <t>Bhutan</t>
+  </si>
+  <si>
+    <t>CHN</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>FJI</t>
+  </si>
+  <si>
+    <t>Fiji</t>
+  </si>
+  <si>
+    <t>FSM</t>
+  </si>
+  <si>
+    <t>Micronesia (Federated States of)</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>Hong Kong</t>
+  </si>
+  <si>
+    <t>IDN</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>KHM</t>
+  </si>
+  <si>
+    <t>Cambodia</t>
+  </si>
+  <si>
+    <t>KOR</t>
+  </si>
+  <si>
+    <t>Korea, Republic of</t>
+  </si>
+  <si>
+    <t>LAO</t>
+  </si>
+  <si>
+    <t>Lao People's Democratic Republic</t>
+  </si>
+  <si>
+    <t>LKA</t>
+  </si>
+  <si>
+    <t>Sri Lanka</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>Macao</t>
+  </si>
+  <si>
+    <t>MDV</t>
+  </si>
+  <si>
+    <t>Maldives</t>
+  </si>
+  <si>
+    <t>MMR</t>
+  </si>
+  <si>
+    <t>Myanmar</t>
+  </si>
+  <si>
+    <t>MNG</t>
+  </si>
+  <si>
+    <t>Mongolia</t>
+  </si>
+  <si>
+    <t>MYS</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>NCL</t>
+  </si>
+  <si>
+    <t>New Caledonia</t>
+  </si>
+  <si>
+    <t>NPL</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
+    <t>PAK</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>PHL</t>
+  </si>
+  <si>
+    <t>Philippines</t>
+  </si>
+  <si>
+    <t>PNG</t>
+  </si>
+  <si>
+    <t>Papua New Guinea</t>
+  </si>
+  <si>
+    <t>PRK</t>
+  </si>
+  <si>
+    <t>Korea (Democratic People's Republic of)</t>
+  </si>
+  <si>
+    <t>PYF</t>
+  </si>
+  <si>
+    <t>French Polynesia</t>
+  </si>
+  <si>
+    <t>SGP</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>Solomon Islands</t>
+  </si>
+  <si>
+    <t>THA</t>
+  </si>
+  <si>
+    <t>Thailand</t>
+  </si>
+  <si>
+    <t>TLS</t>
+  </si>
+  <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>Taiwan, Province of China</t>
+  </si>
+  <si>
+    <t>VNM</t>
+  </si>
+  <si>
+    <t>Viet Nam</t>
+  </si>
+  <si>
+    <t>VUT</t>
+  </si>
+  <si>
+    <t>Vanuatu</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>Samoa</t>
+  </si>
+  <si>
+    <t>ABW</t>
+  </si>
+  <si>
+    <t>Aruba</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>BHS</t>
+  </si>
+  <si>
+    <t>Bahamas</t>
+  </si>
+  <si>
+    <t>BLZ</t>
+  </si>
+  <si>
+    <t>Belize</t>
+  </si>
+  <si>
+    <t>BOL</t>
+  </si>
+  <si>
+    <t>Bolivia (Plurinational State of)</t>
+  </si>
+  <si>
+    <t>BRA</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>BRB</t>
+  </si>
+  <si>
+    <t>Barbados</t>
+  </si>
+  <si>
+    <t>CHL</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>CRI</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>CUB</t>
+  </si>
+  <si>
+    <t>Cuba</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t>Dominican Republic</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>GLP</t>
+  </si>
+  <si>
+    <t>Guadeloupe</t>
+  </si>
+  <si>
+    <t>GRD</t>
+  </si>
+  <si>
+    <t>Grenada</t>
+  </si>
+  <si>
+    <t>GTM</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>GUF</t>
+  </si>
+  <si>
+    <t>French Guiana</t>
+  </si>
+  <si>
+    <t>GUY</t>
+  </si>
+  <si>
+    <t>Guyana</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>Honduras</t>
+  </si>
+  <si>
+    <t>HTI</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>JAM</t>
+  </si>
+  <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <t>MTQ</t>
+  </si>
+  <si>
+    <t>Martinique</t>
+  </si>
+  <si>
+    <t>NIC</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>Peru</t>
+  </si>
+  <si>
+    <t>PRY</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
+    <t>SUR</t>
+  </si>
+  <si>
+    <t>Suriname</t>
+  </si>
+  <si>
+    <t>TTO</t>
+  </si>
+  <si>
+    <t>Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t>URY</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>VEN</t>
+  </si>
+  <si>
+    <t>Venezuela (Bolivarian Republic of)</t>
+  </si>
+  <si>
+    <t>VIR</t>
+  </si>
+  <si>
+    <t>Virgin Islands (U.S.)</t>
+  </si>
+  <si>
+    <t>AGO</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>ARE</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
+    <t>BDI</t>
+  </si>
+  <si>
+    <t>Burundi</t>
+  </si>
+  <si>
+    <t>BEN</t>
+  </si>
+  <si>
+    <t>Benin</t>
+  </si>
+  <si>
+    <t>BFA</t>
+  </si>
+  <si>
+    <t>Burkina Faso</t>
+  </si>
+  <si>
+    <t>BHR</t>
+  </si>
+  <si>
+    <t>Bahrain</t>
+  </si>
+  <si>
+    <t>BWA</t>
+  </si>
+  <si>
+    <t>Botswana</t>
+  </si>
+  <si>
+    <t>CAF</t>
+  </si>
+  <si>
+    <t>Central African Republic</t>
+  </si>
+  <si>
+    <t>CIV</t>
+  </si>
+  <si>
+    <t>Ivory Coast</t>
+  </si>
+  <si>
+    <t>CMR</t>
+  </si>
+  <si>
+    <t>Cameroon</t>
+  </si>
+  <si>
+    <t>COD</t>
+  </si>
+  <si>
+    <t>Congo, Democratic Republic of the</t>
+  </si>
+  <si>
+    <t>COG</t>
+  </si>
+  <si>
+    <t>Congo</t>
+  </si>
+  <si>
+    <t>COM</t>
+  </si>
+  <si>
+    <t>Comoros</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>Cabo Verde</t>
+  </si>
+  <si>
+    <t>DJI</t>
+  </si>
+  <si>
+    <t>Djibouti</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
+    <t>EGY</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>ERI</t>
+  </si>
+  <si>
+    <t>Eritrea</t>
+  </si>
+  <si>
+    <t>ESH</t>
+  </si>
+  <si>
+    <t>Western Sahara</t>
+  </si>
+  <si>
+    <t>ETH</t>
+  </si>
+  <si>
+    <t>Ethiopia</t>
+  </si>
+  <si>
+    <t>GAB</t>
+  </si>
+  <si>
+    <t>Gabon</t>
+  </si>
+  <si>
+    <t>GHA</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>GIN</t>
+  </si>
+  <si>
+    <t>Guinea</t>
+  </si>
+  <si>
+    <t>GMB</t>
+  </si>
+  <si>
+    <t>Gambia</t>
+  </si>
+  <si>
+    <t>GNB</t>
+  </si>
+  <si>
+    <t>Guinea-Bissau</t>
+  </si>
+  <si>
+    <t>GNQ</t>
+  </si>
+  <si>
+    <t>Equatorial Guinea</t>
+  </si>
+  <si>
+    <t>IRN</t>
+  </si>
+  <si>
+    <t>Iran (Islamic Republic of)</t>
+  </si>
+  <si>
+    <t>IRQ</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>ISR</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>JOR</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>KEN</t>
+  </si>
+  <si>
+    <t>Kenya</t>
+  </si>
+  <si>
+    <t>KWT</t>
+  </si>
+  <si>
+    <t>Kuwait</t>
+  </si>
+  <si>
+    <t>LBN</t>
+  </si>
+  <si>
+    <t>Lebanon</t>
+  </si>
+  <si>
+    <t>LBR</t>
+  </si>
+  <si>
+    <t>Liberia</t>
+  </si>
+  <si>
+    <t>LBY</t>
+  </si>
+  <si>
+    <t>Libya</t>
+  </si>
+  <si>
+    <t>LSO</t>
+  </si>
+  <si>
+    <t>Lesotho</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>MDG</t>
+  </si>
+  <si>
+    <t>Madagascar</t>
+  </si>
+  <si>
+    <t>MLI</t>
+  </si>
+  <si>
+    <t>Mali</t>
+  </si>
+  <si>
+    <t>MOZ</t>
+  </si>
+  <si>
+    <t>Mozambique</t>
+  </si>
+  <si>
+    <t>MRT</t>
+  </si>
+  <si>
+    <t>Mauritania</t>
+  </si>
+  <si>
+    <t>MUS</t>
+  </si>
+  <si>
+    <t>Mauritius</t>
+  </si>
+  <si>
+    <t>MWI</t>
+  </si>
+  <si>
+    <t>Malawi</t>
+  </si>
+  <si>
+    <t>MYT</t>
+  </si>
+  <si>
+    <t>Mayotte</t>
+  </si>
+  <si>
+    <t>NAM</t>
+  </si>
+  <si>
+    <t>Namibia</t>
+  </si>
+  <si>
+    <t>NER</t>
+  </si>
+  <si>
+    <t>Niger</t>
+  </si>
+  <si>
+    <t>NGA</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>OMN</t>
+  </si>
+  <si>
+    <t>Oman</t>
+  </si>
+  <si>
+    <t>PSE</t>
+  </si>
+  <si>
+    <t>Palestine, State of</t>
+  </si>
+  <si>
+    <t>QAT</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>REU</t>
+  </si>
+  <si>
+    <t>Reunion Islands</t>
+  </si>
+  <si>
+    <t>RWA</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>SAU</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>SDN</t>
+  </si>
+  <si>
+    <t>Sudan</t>
+  </si>
+  <si>
+    <t>SEN</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>SLE</t>
+  </si>
+  <si>
+    <t>Sierra Leone</t>
+  </si>
+  <si>
+    <t>SOM</t>
+  </si>
+  <si>
+    <t>Somalia</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
+    <t>STP</t>
+  </si>
+  <si>
+    <t>Sao Tome and Principe</t>
+  </si>
+  <si>
+    <t>SWZ</t>
+  </si>
+  <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
+    <t>SYR</t>
+  </si>
+  <si>
+    <t>Syrian Arab Republic</t>
+  </si>
+  <si>
+    <t>TCD</t>
+  </si>
+  <si>
+    <t>Chad</t>
+  </si>
+  <si>
+    <t>TGO</t>
+  </si>
+  <si>
+    <t>Togo</t>
+  </si>
+  <si>
+    <t>TUN</t>
+  </si>
+  <si>
+    <t>Tunisia</t>
+  </si>
+  <si>
+    <t>TZA</t>
+  </si>
+  <si>
+    <t>Tanzania, United Republic of</t>
+  </si>
+  <si>
+    <t>UGA</t>
+  </si>
+  <si>
+    <t>Uganda</t>
+  </si>
+  <si>
+    <t>YEM</t>
+  </si>
+  <si>
+    <t>Yemen</t>
+  </si>
+  <si>
+    <t>ZAF</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>ZMB</t>
+  </si>
+  <si>
+    <t>Zambia</t>
+  </si>
+  <si>
+    <t>ZWE</t>
+  </si>
+  <si>
+    <t>Zimbabwe</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>Albania</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>BIH</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>CHE</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>GUM</t>
+  </si>
+  <si>
+    <t>Guam</t>
+  </si>
+  <si>
+    <t>ISL</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>MKD</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
+    <t>MNE</t>
+  </si>
+  <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>NZL</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>Puerto Rico</t>
+  </si>
+  <si>
+    <t>SRB</t>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>TUR</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>Armenia</t>
+  </si>
+  <si>
+    <t>AZE</t>
+  </si>
+  <si>
+    <t>Azerbaijan</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>Belarus</t>
+  </si>
+  <si>
+    <t>GEO</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
+    <t>Kazakhstan</t>
+  </si>
+  <si>
+    <t>KGZ</t>
+  </si>
+  <si>
+    <t>Kyrgyzstan</t>
+  </si>
+  <si>
+    <t>MDA</t>
+  </si>
+  <si>
+    <t>Moldova, Republic of</t>
+  </si>
+  <si>
+    <t>RUS</t>
+  </si>
+  <si>
+    <t>Russian Federation</t>
+  </si>
+  <si>
+    <t>TJK</t>
+  </si>
+  <si>
+    <t>Tajikistan</t>
+  </si>
+  <si>
+    <t>TKM</t>
+  </si>
+  <si>
+    <t>Turkmenistan</t>
+  </si>
+  <si>
+    <t>UKR</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>UZB</t>
+  </si>
+  <si>
+    <t>Uzbekistan</t>
+  </si>
+  <si>
+    <t>AIA</t>
+  </si>
+  <si>
+    <t>ATA</t>
+  </si>
+  <si>
+    <t>ATG</t>
+  </si>
+  <si>
+    <t>BES</t>
+  </si>
+  <si>
+    <t>BLM</t>
+  </si>
+  <si>
+    <t>CUW</t>
+  </si>
+  <si>
+    <t>DMA</t>
+  </si>
+  <si>
+    <t>FLK</t>
+  </si>
+  <si>
+    <t>FRO</t>
+  </si>
+  <si>
+    <t>GGY</t>
+  </si>
+  <si>
+    <t>GIB</t>
+  </si>
+  <si>
+    <t>GRL</t>
+  </si>
+  <si>
+    <t>IMN</t>
+  </si>
+  <si>
+    <t>JEY</t>
+  </si>
+  <si>
+    <t>KNA</t>
+  </si>
+  <si>
+    <t>LCA</t>
+  </si>
+  <si>
+    <t>LIE</t>
+  </si>
+  <si>
+    <t>MCO</t>
+  </si>
+  <si>
+    <t>NFK</t>
+  </si>
+  <si>
+    <t>SGS</t>
+  </si>
+  <si>
+    <t>SJM</t>
+  </si>
+  <si>
+    <t>SMR</t>
+  </si>
+  <si>
+    <t>SPM</t>
+  </si>
+  <si>
+    <t>SXM</t>
+  </si>
+  <si>
+    <t>TCA</t>
+  </si>
+  <si>
+    <t>UMI</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>VCT</t>
+  </si>
+  <si>
+    <t>VGB</t>
+  </si>
+  <si>
+    <t>XAD</t>
+  </si>
+  <si>
+    <t>XCA</t>
+  </si>
+  <si>
+    <t>XPI</t>
+  </si>
+  <si>
+    <t>XSP</t>
+  </si>
+  <si>
+    <t>ZNC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +1334,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -353,7 +1431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -370,11 +1448,29 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
@@ -466,15 +1562,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AB4D56B-7E3C-884A-A57F-A003541E2DB8}" name="Table1" displayName="Table1" ref="A1:C30" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AB4D56B-7E3C-884A-A57F-A003541E2DB8}" name="Table1" displayName="Table1" ref="A1:C30" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:C30" xr:uid="{1AB4D56B-7E3C-884A-A57F-A003541E2DB8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C30">
     <sortCondition descending="1" ref="C1:C30"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A76063E7-B7D5-6F44-8A3D-2DE1CAD6EBE9}" name="Code" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{564F38C7-6F0B-9141-9184-5C01A142A27B}" name="Country" dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{B260082B-FC9E-604B-9AAD-A22A788A0506}" name="Potential Storage (Gt)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{A76063E7-B7D5-6F44-8A3D-2DE1CAD6EBE9}" name="Code" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{564F38C7-6F0B-9141-9184-5C01A142A27B}" name="Country" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{B260082B-FC9E-604B-9AAD-A22A788A0506}" name="Potential Storage (Gt)" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -487,6 +1583,18 @@
     <tableColumn id="1" xr3:uid="{5DE130F8-3FBF-C24F-88DA-6FA0D992FAD5}" name="Code"/>
     <tableColumn id="2" xr3:uid="{0573E16B-5F3F-7248-B022-373A83576E64}" name="Country"/>
     <tableColumn id="3" xr3:uid="{CB78F4ED-938B-0E4E-9A71-9EBAEAE968CA}" name="Potential Storage (Gt)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AD469F24-D48B-430E-A7BE-7A40448AB52E}" name="Tabelle3" displayName="Tabelle3" ref="A1:C228" totalsRowShown="0">
+  <autoFilter ref="A1:C228" xr:uid="{AD469F24-D48B-430E-A7BE-7A40448AB52E}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{F1749EB0-C6DE-4DAD-ABAA-CD7C61CD4C0B}" name="Code" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{1B46BB80-AA78-4995-B9EA-046D0334FF99}" name="Country" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{8D18AD11-31FA-40AB-8A13-FF83A2CD5158}" name="Potential Storage (Gt)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -756,9 +1864,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B035BFD-1BD3-2645-9AA1-F56901FBB1C8}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="29.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="29.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>59</v>
       </c>
@@ -769,7 +1877,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
@@ -780,7 +1888,7 @@
         <v>8.9017297420000006</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -791,7 +1899,7 @@
         <v>6.9474020039999997</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>45</v>
       </c>
@@ -802,7 +1910,7 @@
         <v>4.6686674740000003</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>37</v>
       </c>
@@ -813,7 +1921,7 @@
         <v>3.6033377170000001</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -824,7 +1932,7 @@
         <v>3.062954408</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -835,7 +1943,7 @@
         <v>1.9837426360000001</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -846,7 +1954,7 @@
         <v>1.9161548879999999</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
@@ -857,7 +1965,7 @@
         <v>1.8791301039999999</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -868,7 +1976,7 @@
         <v>1.8310086879999998</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>33</v>
       </c>
@@ -879,7 +1987,7 @@
         <v>1.600197353</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -890,7 +1998,7 @@
         <v>1.308291906</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>47</v>
       </c>
@@ -901,7 +2009,7 @@
         <v>1.2606488659999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -912,7 +2020,7 @@
         <v>0.88219997699999997</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -923,7 +2031,7 @@
         <v>0.58415423399999999</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>53</v>
       </c>
@@ -934,7 +2042,7 @@
         <v>0.57342807799999995</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -945,7 +2053,7 @@
         <v>0.42391875600000001</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
@@ -956,7 +2064,7 @@
         <v>0.40063056999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -967,7 +2075,7 @@
         <v>0.39869689600000002</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
@@ -978,7 +2086,7 @@
         <v>0.247208761</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>51</v>
       </c>
@@ -989,7 +2097,7 @@
         <v>2.3345825000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
@@ -1000,7 +2108,7 @@
         <v>2.1748263E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
@@ -1011,7 +2119,7 @@
         <v>3.7213110000000001E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -1022,7 +2130,7 @@
         <v>6.7000000000000002E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
@@ -1033,7 +2141,7 @@
         <v>1.13E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>55</v>
       </c>
@@ -1044,7 +2152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>49</v>
       </c>
@@ -1055,7 +2163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>39</v>
       </c>
@@ -1066,7 +2174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -1077,7 +2185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
@@ -1100,14 +2208,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17615879-9F44-B24B-BC0C-9587452E6B69}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>59</v>
       </c>
@@ -1118,7 +2226,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>61</v>
       </c>
@@ -1129,7 +2237,7 @@
         <v>24.58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>63</v>
       </c>
@@ -1140,7 +2248,7 @@
         <v>69.89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -1157,4 +2265,2528 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD5F6D1-4F86-4DC9-B46B-DF573707EE48}">
+  <dimension ref="A1:C228"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="21.26953125" style="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.14548407399999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="13">
+        <v>2.809580092</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0.47914714399999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="13">
+        <v>57.060989169999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="13">
+        <v>38.303045187999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="13">
+        <v>10.653741557</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="13">
+        <v>1.9083867449999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="13">
+        <v>2.305115458</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0.111482993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="13">
+        <v>0.54412260299999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="13">
+        <v>7.1147191670000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="13">
+        <v>0.13848711599999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="13">
+        <v>11.824961203999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="13">
+        <v>7.0142659999999999E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="13">
+        <v>2.0757197810000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="13">
+        <v>1.7044529980000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="13">
+        <v>5.6111844279999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="13">
+        <v>1.9715175000000001E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="13">
+        <v>5.4663508999999999E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="13">
+        <v>6.9664686180000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="13">
+        <v>1.530281201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="13">
+        <v>11.402393503000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="13">
+        <v>5.5630799999999998E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" s="13">
+        <v>1.22E-6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" s="13">
+        <v>36.236625879999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" s="13">
+        <v>6.4760965779999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="13">
+        <v>0.47966230500000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="13">
+        <v>5.7838343280000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="13">
+        <v>79.986028619999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="13">
+        <v>2.2112095199999997</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C44" s="13">
+        <v>6.4962536330000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="13">
+        <v>5.3474409000000001E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="13">
+        <v>0.92061940399999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="13">
+        <v>4.9352249999999997E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" s="13">
+        <v>0.51554142599999997</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="13">
+        <v>4.1800000000000001E-7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="13">
+        <v>8.5252233999999996E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="13">
+        <v>0.71657401799999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" s="13">
+        <v>2.1054100999999999E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" s="13">
+        <v>1.640141965</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" s="13">
+        <v>2.5926229410000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C55" s="13">
+        <v>2.6610751100000002E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C56" s="13">
+        <v>0.34889811999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="13">
+        <v>24.58087493</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C58" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C59" s="13">
+        <v>3.6336583359999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" s="13">
+        <v>0.134164529</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C61" s="13">
+        <v>5.6951576809999995</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C62" s="13">
+        <v>6.5189418449999996</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C63" s="13">
+        <v>0.76612453600000008</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C64" s="13">
+        <v>2.9714845997000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" s="13">
+        <v>1.0526468226999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C66" s="13">
+        <v>1.6490487570000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C67" s="13">
+        <v>5.5871377689999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C69" s="13">
+        <v>10.456584855999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C70" s="13">
+        <v>4.90296705</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C71" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C72" s="13">
+        <v>0.124979534</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C74" s="13">
+        <v>0.13274288400000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C75" s="13">
+        <v>3.9793770899999998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C76" s="13">
+        <v>0.41429087999999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C77" s="13">
+        <v>0.22920881500000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C78" s="13">
+        <v>0.410295505</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C79" s="13">
+        <v>35.297473025999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C80" s="13">
+        <v>1.7535441679999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C81" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C82" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C83" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C84" s="13">
+        <v>44.893042248</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C85" s="13">
+        <v>16.812533835</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C86" s="13">
+        <v>1.1603532010000002</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C87" s="13">
+        <v>5.4723136439999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C88" s="13">
+        <v>8.1893392019999993</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C89" s="13">
+        <v>2.1484820469999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C90" s="13">
+        <v>1.6077469149999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C91" s="13">
+        <v>1.46491847</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="13">
+        <v>0.29289983600000002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C93" s="13">
+        <v>1.7392195509999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C94" s="13">
+        <v>0.58212976900000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C95" s="13">
+        <v>4.4465998779999998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C96" s="13">
+        <v>8.5923432220000002</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C97" s="13">
+        <v>1.6701503999999999E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C98" s="13">
+        <v>1.032602974</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C99" s="13">
+        <v>7.6207352950000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C100" s="13">
+        <v>0.60290633999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C101" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C102" s="13">
+        <v>0.21249326900000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C103" s="13">
+        <v>42.900870748000003</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C104" s="13">
+        <v>5.2529495000000002E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C105" s="13">
+        <v>4.2084363840000005</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C106" s="13">
+        <v>10.085913471</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C107" s="13">
+        <v>19.364305000000002</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C108" s="13">
+        <v>10.042978527000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C109" s="13">
+        <v>21.493156477000003</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C110" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C111" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C112" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C113" s="13">
+        <v>8.4836368929999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C114" s="13">
+        <v>9.6342648519999994</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C115" s="13">
+        <v>6.1407401729999993</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C116" s="13">
+        <v>5.2728227800000003</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C117" s="13">
+        <v>2.0916255000000002E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C118" s="13">
+        <v>2.166027894</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C119" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C120" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C121" s="13">
+        <v>34.861437756999997</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C122" s="13">
+        <v>5.4493949379999993</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C123" s="13">
+        <v>3.071654412</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C124" s="13">
+        <v>0.50510465500000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C125" s="13">
+        <v>22.702655777</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C126" s="13">
+        <v>6.3978439250000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C127" s="13">
+        <v>7.7765791000000001E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C128" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C129" s="13">
+        <v>1.6298813409999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C130" s="13">
+        <v>7.2632189670000002</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C131" s="13">
+        <v>3.3627180000000002E-3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C132" s="13">
+        <v>5.4576007860000004</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C133" s="13">
+        <v>3.065387758</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C134" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C135" s="13">
+        <v>3.2905538819999998</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C136" s="13">
+        <v>13.030283435000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C137" s="13">
+        <v>0.93022705500000002</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C138" s="13">
+        <v>1.0548236000000001E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C139" s="13">
+        <v>0.33044347299999999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C140" s="13">
+        <v>112.46362535</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C141" s="13">
+        <v>1.13E-5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C142" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C143" s="13">
+        <v>0.57342807799999995</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C144" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C145" s="13">
+        <v>69.890703510000009</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C146" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C147" s="13">
+        <v>2.3345825000000001E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C148" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C149" s="13">
+        <v>1.2606488659999999</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C150" s="13">
+        <v>4.6686674740000003</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C151" s="13">
+        <v>1.8791301039999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C152" s="13">
+        <v>3.7213110000000001E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C153" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C154" s="13">
+        <v>3.6033377170000001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C155" s="13">
+        <v>8.9017297420000006</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C156" s="13">
+        <v>1.600197353</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C157" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C158" s="13">
+        <v>1.308291906</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C159" s="13">
+        <v>2.1748263E-2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" s="13">
+        <v>3.062954408</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C161" s="13">
+        <v>6.926115E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C162" s="13">
+        <v>1.9837426360000001</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C163" s="13">
+        <v>3.0234711289999998</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C164" s="13">
+        <v>0.42391875600000001</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C165" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C166" s="13">
+        <v>0.39869689600000002</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C167" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" s="13">
+        <v>0.58415423399999999</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C169" s="13">
+        <v>0.17497823900000001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C170" s="13">
+        <v>1.8310086879999998</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C171" s="13">
+        <v>6.9474020039999997</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C172" s="13">
+        <v>4.8264716949999995</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" s="13">
+        <v>1.9161548879999999</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C174" s="13">
+        <v>1.9299999999999999E-7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C175" s="13">
+        <v>0.40063056999999996</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" s="13">
+        <v>0.88219997699999997</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C177" s="13">
+        <v>5.2713830000000001E-3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C178" s="13">
+        <v>6.7000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C179" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C180" s="13">
+        <v>0.247208761</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C181" s="13">
+        <v>1.187206419</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C182" s="13">
+        <v>140.82564743</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C183" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C184" s="13">
+        <v>1.1600000000000001E-5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C185" s="13">
+        <v>0.55298445699999998</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C186" s="13">
+        <v>7.5224013999999992E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C187" s="13">
+        <v>32.228346019999996</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C188" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C189" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C190" s="13">
+        <v>244.15848018</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C191" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C192" s="13">
+        <v>13.660396049999999</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C193" s="13">
+        <v>2.5686338219999998</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C194" s="13">
+        <v>4.5085753049999999</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C195" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C196" s="13">
+        <v>2.1179987000000001E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C197" s="13">
+        <v>7.1334666599999999E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C198" s="13">
+        <v>1.1444517E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C199" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C200" s="13">
+        <v>2.0217260000000001E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C201" s="13">
+        <v>9.0445820000000007E-3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C202" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C203" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C204" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C205" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C206" s="13">
+        <v>2.1655269000000001E-2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C207" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C208" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C209" s="13">
+        <v>3.6008580000000002E-3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C210" s="13">
+        <v>1.2126513E-2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C211" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C212" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C213" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C214" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C215" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C216" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C217" s="13">
+        <v>5.5201180000000001E-3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C218" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C219" s="13">
+        <v>1.2234471E-2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C220" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C221" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C222" s="13">
+        <v>4.0472598999999998E-2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C223" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C224" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C225" s="13">
+        <v>14.89015249</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C226" s="13">
+        <v>2.0421600000000001E-4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C227" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C228" s="13">
+        <v>6.1099999999999995E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>